--- a/www/download/COUNTRY.SVK.rpA2.xlsx
+++ b/www/download/COUNTRY.SVK.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Eslováquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.985998871219229</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.01726276463438</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.1157227322029</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.16924873131231</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.39161406895718</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.52218588940335</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.60446667405649</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1.49992492877326</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.21805641823749</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.06910708892009</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.02787598364932</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.983671143712093</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.817768599041415</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.70587963903473</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.716948688620144</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>8.15637767860715</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.151</t>
+          <t>7.19464109944721</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.129</t>
+          <t>7.59037198238944</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>7.71799505147452</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.065</t>
+          <t>7.82822658909221</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>7.30844089934705</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.037</t>
+          <t>7.32440968899932</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.038</t>
+          <t>7.7343984954424</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>6.8658912284145</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>5.08493584789378</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.089</t>
+          <t>4.91797314397087</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>4.5854208585153</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>4.00405675010057</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>4.06498785310179</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>3.18325431489819</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>4.83158770418826</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.011</t>
+          <t>4.53610625196598</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>4.64625973085063</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>4.61251011106848</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>4.95273840175338</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>4.74555020537083</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>4.56025038484924</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>4.5129788070739</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>3.84189329914575</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>3.10613698158648</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>3.17275213631016</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>2.96064829648802</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>2.31523902358495</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>2.42520140405947</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.848</t>
+          <t>1.78079506246257</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3956.528</t>
+          <t>2.16213130748618</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3962.421</t>
+          <t>2.00423043006803</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3915.031</t>
+          <t>2.08913253825296</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3833.549</t>
+          <t>2.0537694029171</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3735.161</t>
+          <t>2.24658805575329</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3675.511</t>
+          <t>2.30078638477778</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3644.524</t>
+          <t>2.17856171624287</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3539.907</t>
+          <t>2.16321118352325</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3463.997</t>
+          <t>0.680754738168865</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3555.952</t>
+          <t>1.35211790639642</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3679.17</t>
+          <t>1.43117560565327</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3728.418</t>
+          <t>1.32512935289784</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3883.844</t>
+          <t>0.923241157021382</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4039.07</t>
+          <t>0.627141384892507</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3988.091</t>
+          <t>0.287848183547563</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3551.322</t>
+          <t>13983853362.5552</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3557.791</t>
+          <t>14260502686.4047</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3511.601</t>
+          <t>13193623056.9322</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3439.541</t>
+          <t>12917828876.409</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3305.355</t>
+          <t>12416863496.3987</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3225.975</t>
+          <t>12204930325.4562</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3198.825</t>
+          <t>12365721327.2823</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3099.35</t>
+          <t>11987488691.8728</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2995.506</t>
+          <t>12360525163.6691</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2990.358</t>
+          <t>12590710920.4697</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3077.563</t>
+          <t>13179558393.8795</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3106.024</t>
+          <t>13905642307.0667</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3213.605</t>
+          <t>15343642747.0696</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3258.575</t>
+          <t>15779604395.9097</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3049.539</t>
+          <t>15162285410.0688</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>1608224174.7094</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>1713112945.01253</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>1650690360.41927</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>1624462440.68883</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>1488555583.97504</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>1517369860.70355</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>1547820414.38602</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>1501869994.82714</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>1686745912.17149</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>1998824626.5592</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>2066717606.45779</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>2209934469.25613</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>2675812426.70286</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>2662261954.01187</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>3084896159.13777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>11110319.5050898</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>10378946.1845602</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>9772401.23712986</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>9054648.65265102</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>10005261.0549007</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>9602956.00854618</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>9178269.61684327</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>7751469.05198595</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>5945927.11985315</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>77.11</t>
+          <t>5198526.28670237</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.24</t>
+          <t>4887083.01978389</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>4422379.67802996</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>3640105.80351971</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>4077730.11587218</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>4630837.46169239</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>31516.9339629052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>30387.6253982497</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>29480.4574632551</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>28247.8981134842</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>27970.8754612427</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>27492.5160206785</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>26346.8709781178</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>25451.6588239393</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>26645.7151134492</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>29955.5987475983</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>32249.9535994165</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>33273.6181592595</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>38425.2427553137</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>43899.8810712481</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>39357.2744135594</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>60999.6565528436</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>62016.4759997378</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>56430.9286861241</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>54570.3126324041</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>54118.8995247181</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>53498.6208693264</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>52287.6640299472</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>51339.9641244162</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>56678.1272922942</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>62618.0503003503</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>69719.5651778484</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>76560.7903990476</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>94702.9538188017</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>106392.953851068</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>94492.1321217319</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>5.34261151164397</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>4.92763719932331</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>5.09649327737962</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>5.10399750171483</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>5.42224912701902</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>5.20999011963246</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>5.07148012731094</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.09</t>
+          <t>5.12979381302793</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>4.32342872025798</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>74.33</t>
+          <t>3.55005332509927</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>3.61044513194175</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>3.38417466563925</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>2.7317022723762</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>2.8192959776664</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>2.1450443772767</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4836.19096461471</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>5701.62837290588</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6135.64293581954</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6877.212381587</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>6487.1615341003</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>5674.46111006042</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>6827.95496708534</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>7746.74847322426</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>9881.98885097931</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>11642.6934697896</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>13410.6979202162</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>14373.2192606829</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>18748.8787394605</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>22017.7754302872</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>20919.2346228943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.985998871219229</t>
+          <t>816.9417490527</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.01726276463438</t>
+          <t>851.960147510448</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1157227322029</t>
+          <t>829.063530142321</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.16924873131231</t>
+          <t>825.100728964437</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.39161406895718</t>
+          <t>783.396706527995</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.52218588940335</t>
+          <t>817.405282320472</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.60446667405649</t>
+          <t>832.985093533885</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.49992492877326</t>
+          <t>810.002397225226</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.21805641823749</t>
+          <t>910.717805660953</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.06910708892009</t>
+          <t>1108.47641636186</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.02787598364932</t>
+          <t>1136.34270140002</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.983671143712093</t>
+          <t>1190.36522633022</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.817768599041415</t>
+          <t>1415.37162547089</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.70587963903473</t>
+          <t>1377.2645179308</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948688620144</t>
+          <t>1669.10294958965</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-275190493.007969</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-300798765.927447</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-701221936.138278</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-503209743.878628</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-374657009.200161</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-299634907.4494</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-454357711.18281</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-252862635.465</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>407074691.729019</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1350158217.19001</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1429058933.50006</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2051838490.24653</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>3410601766.06046</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>3102451965.72754</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>3823165534.12175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-375941517.287049</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-198820723.986686</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-595133187.812104</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-424947047.935175</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-339462513.320397</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-209556608.342371</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-363514722.969673</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-145356119.050902</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>459127272.734835</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1185133547.28713</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1316680713.39451</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1965928792.32864</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>3391629840.80816</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>3243758672.02633</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>3944345808.4941</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>100751024.279079</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-101978041.940761</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-106088748.326173</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-78262695.9434522</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-35194495.8797646</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-90078299.1070291</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-90842988.2131371</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>-107506516.414098</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>-52052581.0058163</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>165024669.902881</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>112378220.105557</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>85909697.9178831</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>18971925.2523076</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>-141306706.298784</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>-121180274.372352</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>5181.54414188421</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5050.11066272391</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>5054.38023803328</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>5036.41278826201</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>5031.16881460899</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>5076.07872694551</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>5057.45244173722</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>4965.14768304898</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>4848.14132270585</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>5043.62680406141</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>5239.04567588728</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>5218.76906813488</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>5281.74551102651</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>5260.18083351576</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>5249.40284670287</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5372.28855222291</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5239.71119476966</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5250.25777975</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5194.25200234315</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5206.34502580142</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5275.82558532917</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5226.95495325545</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>5129.9358815853</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5009.664255616</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>5223.84818075362</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5408.46328758109</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>5401.63684509613</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>5487.51891806791</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>5494.42723991533</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5520.31363950761</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>815.64</t>
+          <t>10351.6164662887</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>719.46</t>
+          <t>10209.7868203828</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>759.04</t>
+          <t>11021.2280981764</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>771.8</t>
+          <t>12467.7816367772</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>782.82</t>
+          <t>11639.4145398027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>730.84</t>
+          <t>13620.6879779712</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>732.44</t>
+          <t>14490.7719792123</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>773.44</t>
+          <t>16402.0952439891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>686.59</t>
+          <t>24339.5612895928</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>508.49</t>
+          <t>30296.9138541655</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>491.8</t>
+          <t>34796.8452333126</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>458.54</t>
+          <t>44573.1727259821</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>400.41</t>
+          <t>61061.8625611863</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>406.5</t>
+          <t>73507.3800417416</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>318.33</t>
+          <t>57239.2583584334</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>483.16</t>
+          <t>3191838212.05929</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>453.61</t>
+          <t>3132772681.29946</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>464.63</t>
+          <t>3172748840.99079</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>461.25</t>
+          <t>3142879672.41298</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>495.27</t>
+          <t>3191833912.27663</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>474.56</t>
+          <t>3624748810.16038</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>456.03</t>
+          <t>3789525787.84569</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>451.3</t>
+          <t>3683091532.41581</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>384.19</t>
+          <t>4109676126.08365</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>310.61</t>
+          <t>4468106969.00185</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>317.28</t>
+          <t>4951795897.17002</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>296.06</t>
+          <t>5716868387.54832</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>231.52</t>
+          <t>6562683526.93046</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>242.52</t>
+          <t>6514426363.23536</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>178.08</t>
+          <t>6052640779.00135</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>216.21</t>
+          <t>9971.94111236904</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>200.42</t>
+          <t>12268.0238295751</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>208.91</t>
+          <t>12608.4577903186</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>205.38</t>
+          <t>14211.7350719905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>224.66</t>
+          <t>12105.0494638383</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>230.08</t>
+          <t>13679.5757818173</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>217.86</t>
+          <t>15893.3534296949</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>216.32</t>
+          <t>17703.8140097263</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>68.08</t>
+          <t>24067.1026816729</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>135.21</t>
+          <t>30326.5043170794</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>143.12</t>
+          <t>35572.909817733</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>132.51</t>
+          <t>45020.0498790437</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>59368.9390783811</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>62.71</t>
+          <t>72874.1417025702</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>55238.9468660171</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11320.454</t>
+          <t>2807461653.17038</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11271.216</t>
+          <t>3411283986.70174</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11177.305</t>
+          <t>2887040623.59556</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11005.966</t>
+          <t>3125542247.02709</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10752.055</t>
+          <t>2951899098.63526</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10682.719</t>
+          <t>3342522617.59132</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10644.762</t>
+          <t>3774444256.06367</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10456.933</t>
+          <t>3837199725.73952</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10322.258</t>
+          <t>4436077857.6006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10738.806</t>
+          <t>5826388563.72585</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11297.809</t>
+          <t>6579280628.33827</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>11518.391</t>
+          <t>7873714768.16904</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11946.17</t>
+          <t>9620112818.00879</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>12430.009</t>
+          <t>9497396747.42246</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>12427.229</t>
+          <t>9454917173.60784</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10200.341</t>
+          <t>379.675353919671</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10154.712</t>
+          <t>-2058.23700919231</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10063.423</t>
+          <t>-1587.22969214215</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9915.715</t>
+          <t>-1743.95343521331</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9559.875</t>
+          <t>-465.634924035594</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9422.852</t>
+          <t>-58.8878038461029</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9397.561</t>
+          <t>-1402.58145048259</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9206.153</t>
+          <t>-1301.71876573727</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8979.272</t>
+          <t>272.458607919924</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9094.759</t>
+          <t>-29.5904629139157</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9528.488</t>
+          <t>-776.064584420391</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9688.739</t>
+          <t>-446.877153061536</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>9985.335</t>
+          <t>1692.92348280518</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10167.966</t>
+          <t>633.238339171445</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9702.135</t>
+          <t>2000.31149241636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13983.853</t>
+          <t>384376558.888909</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14260.503</t>
+          <t>-278511305.402284</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13193.623</t>
+          <t>285708217.395231</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12917.829</t>
+          <t>17337425.3858933</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12416.863</t>
+          <t>239934813.641372</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12204.93</t>
+          <t>282226192.569052</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12365.721</t>
+          <t>15081531.7820184</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11987.489</t>
+          <t>-154108193.32371</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12360.525</t>
+          <t>-326401731.516946</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12590.711</t>
+          <t>-1358281594.724</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13179.558</t>
+          <t>-1627484731.16825</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13905.642</t>
+          <t>-2156846380.62073</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>15343.643</t>
+          <t>-3057429291.07834</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>15779.604</t>
+          <t>-2982970384.1871</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>15162.285</t>
+          <t>-3402276394.60648</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>9949.73537</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>11076.07584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>10484.77652</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>10822.72855</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>9856.07718</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9877.84729</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>10295.9501</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>11708.89663</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>15736.3511</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>19759.02915</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>22007.46628</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>26347.03686</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>35727.13067</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>45312.27975</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>39378.88229</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7225.093</t>
+          <t>0.090748847984198</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6987.543</t>
+          <t>0.0792387016025794</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6892.569</t>
+          <t>0.0700384931463449</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6686.814</t>
+          <t>0.0618776921599689</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6417.546</t>
+          <t>0.0597925803915121</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6272.017</t>
+          <t>0.0701091127758251</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6230.878</t>
+          <t>0.0626623839208485</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5942.768</t>
+          <t>0.0654072210007268</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5810.972</t>
+          <t>0.0725551337240385</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>6023.22</t>
+          <t>0.0832771275182665</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>6096.426</t>
+          <t>0.0805325673570078</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6043.446</t>
+          <t>0.0972976531718734</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6225.605</t>
+          <t>0.104835879881524</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6510.983</t>
+          <t>0.113964217768146</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6315.301</t>
+          <t>0.0994072733229005</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>5894.25037387876</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>6603.75080997851</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>7040.07879467815</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>7300.48399943145</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6386.01976775629</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6408.69031067664</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>6434.05720682011</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>7438.84156967545</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>9969.87089404469</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>12063.8341282007</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>13882.2527629599</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>16059.1275751979</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>21385.5337672559</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>27426.80672863</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>26902.3427813828</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1608.224</t>
+          <t>6561.3869648896</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1713.113</t>
+          <t>7312.97872018727</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1650.69</t>
+          <t>7842.89355693317</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1624.462</t>
+          <t>8135.20634611494</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1488.556</t>
+          <t>7210.15848883682</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1517.37</t>
+          <t>7311.75335210429</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1547.82</t>
+          <t>7333.6971430638</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1501.87</t>
+          <t>8486.40175983047</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1686.746</t>
+          <t>11434.3765778881</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1998.825</t>
+          <t>14226.8452442885</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2066.718</t>
+          <t>16425.3731892327</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2209.934</t>
+          <t>19014.5350364168</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2675.812</t>
+          <t>25613.2077510367</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2662.262</t>
+          <t>32694.8229586497</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3084.896</t>
+          <t>32072.4831027948</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>534.26</t>
+          <t>67974.0340237687</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>492.76</t>
+          <t>76089.0821652557</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>509.65</t>
+          <t>76225.1820023043</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>510.4</t>
+          <t>81488.688512532</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>542.22</t>
+          <t>74666.3660914128</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>75271.0594799448</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>507.15</t>
+          <t>78839.4587108452</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>512.98</t>
+          <t>90809.7029054219</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>432.34</t>
+          <t>117715.378261412</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>355.01</t>
+          <t>142386.934915846</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>361.04</t>
+          <t>158701.616501227</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>338.42</t>
+          <t>176099.21354047</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>273.17</t>
+          <t>224127.269080553</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>281.93</t>
+          <t>275751.31612799</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>271426.315121503</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6561.3869648896</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.379</t>
+          <t>7158.20272882798</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.772</t>
+          <t>8026.97714936827</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9.055</t>
+          <t>8181.77592911671</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.005</t>
+          <t>8034.51778925982</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.603</t>
+          <t>8183.77548044168</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.178</t>
+          <t>8343.3197503356</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7.751</t>
+          <t>8763.44569555475</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.946</t>
+          <t>9272.62748129977</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.199</t>
+          <t>9618.57064797771</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.887</t>
+          <t>10696.1554796788</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>11674.1399216049</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>13244.8694598298</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.078</t>
+          <t>14285.14497636</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.631</t>
+          <t>14160.5412041467</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5894.25037387876</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6470.7072546478</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>7225.14170477271</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7350.23570289687</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>7135.50794459346</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>7169.05179711589</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7301.24692839786</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7657.1766798517</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>8069.40186823319</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>8205.66423332557</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>9107.20554338702</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>9937.39322600055</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>11190.8437912736</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>12162.7748933266</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>12015.158418251</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11004.7562451104</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11730.8284498127</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>11474.3398230668</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>11919.5443638851</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10951.6562311632</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10951.6483078957</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11768.2233969362</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>13686.3587801695</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>18422.8438621119</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>23500.2684057115</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>26191.3465407673</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>31507.2594635832</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>42245.4581989633</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>53443.5584713503</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>47900.9845172052</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10200341163.816</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10154712019.4986</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10063422685.3314</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>9915714679.59419</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>9559874799.70298</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9422851842.79713</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9397560886.59088</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9206153402.26368</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8979271632.63144</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9094758638.366</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9528488127.79162</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9688738712.83564</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>9985335313.17952</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10167966372.4518</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9702135319.77873</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11320454203.5128</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11271216107.0257</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11177305288.8565</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>11005965517.2128</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10752055239.4196</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10682718505.6747</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10644761712.7191</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10456933120.1258</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10322257899.1048</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10738805749.0761</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>11297809271.4509</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>11518390990.4777</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11946169546.5852</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>12430008875.2755</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>12427228613.0919</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7225092859.21636</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6987543336.50031</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6892568532.40042</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6686813696.78546</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6417546282.85426</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6272016681.01793</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6230878169.93828</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5942767540.74077</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5810972378.55502</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6023219861.86919</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6096425667.30265</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6043446390.41681</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6225605153.08768</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6510983399.34685</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6315300694.58071</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2107194</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2151114</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2128906</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2118874</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2065183</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2024843</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2036513</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2038414</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2060469</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2055727</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2088913</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2132389</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2176971</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2262293.83564775</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2251181.62202833</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1968591</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2010790</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1991030</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1968805</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1900130</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1856325</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1858161</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1854155</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1852106</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1803218</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1818745</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1856518</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1890537</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1933007</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1848236</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3956528000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3962421000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3915031000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3833549000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3735161000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3675511000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3644524000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3539907000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3463997000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3555952000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3679170000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3728418000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3883844000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4039070106.46838</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3988090533.37074</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3551322000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3557791000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3511601000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3439541000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3305355000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3225975000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3198825000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3099350000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2995506000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2990358000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3077563000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3106024000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3213605000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3258575000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3049539000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.168935470315182</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.1738213275488</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.17480836933318</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.167515496055335</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.163708469360586</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.192073523559564</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.214433707344593</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.225375204233753</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.215318684569931</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.213480703104851</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.221841624622938</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.773284567686399</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.776372324109149</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.778684350268195</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.791171388899219</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.773020074994206</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.771119572719882</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.752394254379362</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.742645730092074</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.752520864796886</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.746381587509367</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.741808409964212</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0577799619984186</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0498063483420509</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0465072803986258</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.041313115045446</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0632714556452081</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0368069037205545</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0331720382760451</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0319790656741731</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0321604506331831</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0401377093857823</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.03634996541285</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.226144594113496</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.226144594113496</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.226144594113496</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.226144594113496</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.213206625326704</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.214454339777001</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.220203042021981</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.218411694925504</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.229916873864405</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.237779363675329</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.260223879229841</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.27029459181042</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.269389586538394</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.270430175752889</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.282259393564082</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.739375755656045</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.739375755656045</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.739375755656045</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.739375755656045</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.758607201303084</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.760417533827923</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.756460306944286</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.760932507933667</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.750379657492174</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.743270007215774</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.722407010337644</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.71277079806886</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.714076797748988</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.712858725275345</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.703015142324325</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0344796502304585</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0344796502304585</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0344796502304585</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0344796502304585</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0281861733702112</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0251281263950762</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0233366510337324</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0206557971408291</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0197034686434209</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.018950629108897</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0173691104325154</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.01693461012072</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0165336157126178</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.016711098971766</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0147254641115929</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>45337.56892</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>50111.26536</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>50817.40235</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>53365.72453</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>47079.18453</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>49218.95513</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50782.82322</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>58743.00054</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>79164.32126</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>95242.26689</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>107692.82259</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>129809.86542</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>173989.93873</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>222263.09264</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>195303.18255</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17566.14321</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19043.80717</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19317.23338</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>20054.75071</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>18161.81472</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18263.40166</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>19101.92054</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22172.76054</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>29857.22044</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>37727.11365</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>42616.71973</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>50521.7945</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>67858.66595</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>86138.38143</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>79973.46762</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>67022.318965815</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>70576.7592205476</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>74696.0349082144</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>79173.1173978165</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>82159.6337902655</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>84351.6781676676</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>87222.5676832304</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>89935.468029979</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>92321.2550077123</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>94910.7692812392</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>98548.0384099257</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>102713.035738512</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>107404.941944248</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>111919.701274916</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>114233.403024763</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
